--- a/InputData/cost-outputs/DR/Discount Rate.xlsx
+++ b/InputData/cost-outputs/DR/Discount Rate.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="21328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\deept\OneDrive\Desktop\Input Data for India 2.0\cost-outputs\DR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Dropbox (Energy Innovation)\EPS Versions\eps-1.5.0-us-wipI\InputData\cost-outputs\DR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56572341-9847-4027-BE64-09D2D8E180B0}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="75" windowWidth="23955" windowHeight="13605"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -32,31 +31,28 @@
     <t>Discount Rate</t>
   </si>
   <si>
-    <t>Annual Perc</t>
-  </si>
-  <si>
     <t>Notes:</t>
   </si>
   <si>
-    <t>Central Electricity Regulatory Commission</t>
-  </si>
-  <si>
-    <t>technologies for the power sector.  This variable is primarily used by the</t>
-  </si>
-  <si>
-    <t>power sector, to assist in investment decisions, so a power sector rate</t>
-  </si>
-  <si>
-    <t>is the best choice for this variable.</t>
-  </si>
-  <si>
-    <t>http://www.cercind.gov.in/2019/orders/1-SM-2019Suo-Motu.pdf</t>
-  </si>
-  <si>
-    <t>CERC RE Tariff Order 2019-20</t>
-  </si>
-  <si>
-    <t>Page 17, Item 7</t>
+    <t>Interagency Working Group on Social Cost of Carbon, United States Government</t>
+  </si>
+  <si>
+    <t>Technical Update of the Social Cost of Carbon for Regulatory Impact Analysis</t>
+  </si>
+  <si>
+    <t>https://www.whitehouse.gov/sites/default/files/omb/inforeg/scc-tsd-final-july-2015.pdf</t>
+  </si>
+  <si>
+    <t>Page 17, Table A1</t>
+  </si>
+  <si>
+    <t>of Social Cost of Carbon (in the SCoC variable), as well as the discount rate built into the health</t>
+  </si>
+  <si>
+    <t>damages values in the SCoHIbP Social Cost of Health Impacts by Pollutant variable.</t>
+  </si>
+  <si>
+    <t>We choose to use a 3% discount rate here, for consistency with the 3% rate used for the central estimate</t>
   </si>
   <si>
     <t>This is the annual percentage rate by which future savings (e.g. fuel cost savings) are discounted when</t>
@@ -68,16 +64,19 @@
     <t>reasonable for people who are looking to buy fuel-consuming capital equipment, such as industrial</t>
   </si>
   <si>
-    <t xml:space="preserve">equipment or building components. </t>
-  </si>
-  <si>
-    <t>For India, CERC gives a discount rate norm (9.36%) for all</t>
+    <t>equipment or building components. The model works in real dollars, so this rate should be the growth</t>
+  </si>
+  <si>
+    <t>in real value, not the growth in nominal value plus real value.</t>
+  </si>
+  <si>
+    <t>Annual Perc (dimensionless)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -132,7 +131,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -150,55 +149,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>19049</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>161911</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>534408</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>171914</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6E4F123-ABAB-462C-82B1-9114F8768D29}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6553199" y="923911"/>
-          <a:ext cx="5392159" cy="2486503"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -277,23 +227,6 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -329,23 +262,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -521,12 +437,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="52.28515625" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -538,83 +451,85 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" s="2">
-        <v>2019</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B6" r:id="rId1" location="8" display="http://www.whitehouse.gov/omb/circulars_a094#8"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
@@ -625,9 +540,9 @@
     <col min="2" max="2" width="15.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -635,7 +550,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>9.3600000000000003E-2</v>
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>
